--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N66_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N66_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>10.97843509808465</v>
+        <v>1.783995703438755</v>
       </c>
       <c r="D2" t="n">
-        <v>13.14798709098003</v>
+        <v>2.136547902284255</v>
       </c>
       <c r="E2" t="n">
-        <v>15.17940125315326</v>
+        <v>2.466652703637405</v>
       </c>
       <c r="F2" t="n">
-        <v>8.571659865717514</v>
+        <v>1.392894728179096</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>60.89178471503796</v>
+        <v>9.89491501619367</v>
       </c>
       <c r="D3" t="n">
-        <v>30.49174576195022</v>
+        <v>4.954908686316911</v>
       </c>
       <c r="E3" t="n">
-        <v>15.17940125315326</v>
+        <v>2.466652703637405</v>
       </c>
       <c r="F3" t="n">
-        <v>8.571659865717514</v>
+        <v>1.392894728179096</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>67.61312709539122</v>
+        <v>10.98713315300107</v>
       </c>
       <c r="D4" t="n">
-        <v>35.51207544866783</v>
+        <v>5.770712260408523</v>
       </c>
       <c r="E4" t="n">
-        <v>15.17940125315326</v>
+        <v>2.466652703637405</v>
       </c>
       <c r="F4" t="n">
-        <v>8.571659865717514</v>
+        <v>1.392894728179096</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.46597742481803</v>
+        <v>4.62572133153293</v>
       </c>
       <c r="D5" t="n">
-        <v>26.07747084340673</v>
+        <v>4.237589012053594</v>
       </c>
       <c r="E5" t="n">
-        <v>15.17940125315326</v>
+        <v>2.466652703637405</v>
       </c>
       <c r="F5" t="n">
-        <v>8.571659865717514</v>
+        <v>1.392894728179096</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>42.73089299537401</v>
+        <v>6.943770111748276</v>
       </c>
       <c r="D6" t="n">
-        <v>36.89656207738727</v>
+        <v>5.995691337575431</v>
       </c>
       <c r="E6" t="n">
-        <v>15.17940125315326</v>
+        <v>2.466652703637405</v>
       </c>
       <c r="F6" t="n">
-        <v>8.571659865717514</v>
+        <v>1.392894728179096</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>54.5843785117889</v>
+        <v>8.869961508165696</v>
       </c>
       <c r="D7" t="n">
-        <v>30.30702073308683</v>
+        <v>4.924890869126609</v>
       </c>
       <c r="E7" t="n">
-        <v>15.17940125315326</v>
+        <v>2.466652703637405</v>
       </c>
       <c r="F7" t="n">
-        <v>8.571659865717514</v>
+        <v>1.392894728179096</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>54.9156685424716</v>
+        <v>8.923796138151635</v>
       </c>
       <c r="D8" t="n">
-        <v>26.04007687929368</v>
+        <v>4.231512492885223</v>
       </c>
       <c r="E8" t="n">
-        <v>15.17940125315326</v>
+        <v>2.466652703637405</v>
       </c>
       <c r="F8" t="n">
-        <v>8.571659865717514</v>
+        <v>1.392894728179096</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>57.32281281589281</v>
+        <v>9.314957082582582</v>
       </c>
       <c r="D9" t="n">
-        <v>25.69790151271646</v>
+        <v>4.175908995816425</v>
       </c>
       <c r="E9" t="n">
-        <v>15.17940125315326</v>
+        <v>2.466652703637405</v>
       </c>
       <c r="F9" t="n">
-        <v>8.571659865717514</v>
+        <v>1.392894728179096</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>55.31583602822788</v>
+        <v>8.988823354587032</v>
       </c>
       <c r="D10" t="n">
-        <v>24.32492006047109</v>
+        <v>3.952799509826553</v>
       </c>
       <c r="E10" t="n">
-        <v>15.17940125315326</v>
+        <v>2.466652703637405</v>
       </c>
       <c r="F10" t="n">
-        <v>8.571659865717514</v>
+        <v>1.392894728179096</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>32.14385838420407</v>
+        <v>5.223376987433161</v>
       </c>
       <c r="D11" t="n">
-        <v>15.93246319742597</v>
+        <v>2.58902526958172</v>
       </c>
       <c r="E11" t="n">
-        <v>15.17940125315326</v>
+        <v>2.466652703637405</v>
       </c>
       <c r="F11" t="n">
-        <v>8.571659865717514</v>
+        <v>1.392894728179096</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>53.62090069306203</v>
+        <v>8.71339636262258</v>
       </c>
       <c r="D12" t="n">
-        <v>14.98075008941695</v>
+        <v>2.434371889530254</v>
       </c>
       <c r="E12" t="n">
-        <v>15.17940125315326</v>
+        <v>2.466652703637405</v>
       </c>
       <c r="F12" t="n">
-        <v>8.571659865717514</v>
+        <v>1.392894728179096</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>65.24034398894146</v>
+        <v>10.60155589820299</v>
       </c>
       <c r="D13" t="n">
-        <v>34.44301005526668</v>
+        <v>5.596989133980836</v>
       </c>
       <c r="E13" t="n">
-        <v>15.17940125315326</v>
+        <v>2.466652703637405</v>
       </c>
       <c r="F13" t="n">
-        <v>8.571659865717514</v>
+        <v>1.392894728179096</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>58.82241939999083</v>
+        <v>9.55864315249851</v>
       </c>
       <c r="D14" t="n">
-        <v>20.60218100085373</v>
+        <v>3.347854412638731</v>
       </c>
       <c r="E14" t="n">
-        <v>15.17940125315326</v>
+        <v>2.466652703637405</v>
       </c>
       <c r="F14" t="n">
-        <v>8.571659865717514</v>
+        <v>1.392894728179096</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>53.9993245059277</v>
+        <v>8.774890232213252</v>
       </c>
       <c r="D15" t="n">
-        <v>25.47349317434917</v>
+        <v>4.13944264083174</v>
       </c>
       <c r="E15" t="n">
-        <v>15.17940125315326</v>
+        <v>2.466652703637405</v>
       </c>
       <c r="F15" t="n">
-        <v>8.571659865717514</v>
+        <v>1.392894728179096</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>59.06968517616831</v>
+        <v>9.598823841127352</v>
       </c>
       <c r="D16" t="n">
-        <v>35.57231411943864</v>
+        <v>5.780501044408779</v>
       </c>
       <c r="E16" t="n">
-        <v>15.17940125315326</v>
+        <v>2.466652703637405</v>
       </c>
       <c r="F16" t="n">
-        <v>8.571659865717514</v>
+        <v>1.392894728179096</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>69.79494433087464</v>
+        <v>11.34167845376713</v>
       </c>
       <c r="D17" t="n">
-        <v>45.59064977027642</v>
+        <v>7.408480587669919</v>
       </c>
       <c r="E17" t="n">
-        <v>15.17940125315326</v>
+        <v>2.466652703637405</v>
       </c>
       <c r="F17" t="n">
-        <v>8.571659865717514</v>
+        <v>1.392894728179096</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
